--- a/data/availability/projects/mountain-view/mountain-view-crystal.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-crystal.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for mountain-view-crystal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1109,7 +1119,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1120,7 +1129,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1166,7 +1175,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1177,7 +1185,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1223,7 +1231,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1234,7 +1241,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1280,7 +1287,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1291,7 +1297,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1337,7 +1343,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1348,7 +1353,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1394,7 +1399,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1405,7 +1409,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1455,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1462,7 +1465,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1508,7 +1511,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1519,7 +1521,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1565,7 +1567,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1576,7 +1577,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1622,7 +1623,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1679,7 +1679,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1690,7 +1689,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1736,7 +1735,6 @@
       <c r="G13" t="n">
         <v>108.91</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1747,7 +1745,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1793,7 +1791,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1804,7 +1801,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1850,7 +1847,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1861,7 +1857,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1907,7 +1903,6 @@
       <c r="G16" t="n">
         <v>139.26</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1964,7 +1959,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1975,7 +1969,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2021,7 +2015,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2032,7 +2025,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2078,7 +2071,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2089,7 +2081,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2135,7 +2127,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2146,7 +2137,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2192,7 +2183,6 @@
       <c r="G21" t="n">
         <v>111.1</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2203,7 +2193,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2249,7 +2239,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2260,7 +2249,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2306,7 +2295,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2317,7 +2305,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2363,7 +2351,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2374,7 +2361,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2420,7 +2407,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2431,7 +2417,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2477,7 +2463,6 @@
       <c r="G26" t="n">
         <v>139.82</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2488,7 +2473,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2534,7 +2519,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2545,7 +2529,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2591,7 +2575,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2602,7 +2585,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2648,7 +2631,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2659,7 +2641,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2705,7 +2687,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2716,7 +2697,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2762,7 +2743,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2773,7 +2753,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2819,7 +2799,6 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2830,7 +2809,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2876,7 +2855,6 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2887,7 +2865,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2933,7 +2911,6 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2944,7 +2921,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2990,7 +2967,6 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3001,7 +2977,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3047,7 +3023,6 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3058,7 +3033,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3104,7 +3079,6 @@
       <c r="G37" t="n">
         <v>106.41</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3115,7 +3089,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3161,7 +3135,6 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3172,7 +3145,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3218,7 +3191,6 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3229,7 +3201,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3275,7 +3247,6 @@
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3286,7 +3257,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3332,7 +3303,6 @@
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3343,7 +3313,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3389,7 +3359,6 @@
       <c r="G42" t="n">
         <v>168.23</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3400,7 +3369,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3446,7 +3415,6 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3457,7 +3425,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3503,7 +3471,6 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3514,7 +3481,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3560,7 +3527,6 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3571,7 +3537,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3617,7 +3583,6 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3628,7 +3593,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3674,7 +3639,6 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3685,7 +3649,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3731,7 +3695,6 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3742,7 +3705,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3788,7 +3751,6 @@
       <c r="G49" t="n">
         <v>87.12</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3799,7 +3761,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3845,7 +3807,6 @@
       <c r="G50" t="n">
         <v>0</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3856,7 +3817,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3902,7 +3863,6 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3913,7 +3873,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3959,7 +3919,6 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3970,7 +3929,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4016,7 +3975,6 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4027,7 +3985,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4073,7 +4031,6 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4084,7 +4041,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4130,7 +4087,6 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4141,7 +4097,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4187,7 +4143,6 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4198,7 +4153,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4244,7 +4199,6 @@
       <c r="G57" t="n">
         <v>0</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4255,7 +4209,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4301,7 +4255,6 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4312,7 +4265,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4358,7 +4311,6 @@
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4369,7 +4321,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4415,7 +4367,6 @@
       <c r="G60" t="n">
         <v>153.51</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4426,7 +4377,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4472,7 +4423,6 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4483,7 +4433,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4529,7 +4479,6 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4540,7 +4489,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4586,7 +4535,6 @@
       <c r="G63" t="n">
         <v>0</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4597,7 +4545,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4643,7 +4591,6 @@
       <c r="G64" t="n">
         <v>0</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4654,7 +4601,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4700,7 +4647,6 @@
       <c r="G65" t="n">
         <v>131.17</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4711,7 +4657,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4757,7 +4703,6 @@
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4768,7 +4713,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4814,7 +4759,6 @@
       <c r="G67" t="n">
         <v>0</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4825,7 +4769,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4871,7 +4815,6 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4882,7 +4825,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4928,7 +4871,6 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4939,7 +4881,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4985,7 +4927,6 @@
       <c r="G70" t="n">
         <v>0</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4996,7 +4937,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5042,7 +4983,6 @@
       <c r="G71" t="n">
         <v>0</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5053,7 +4993,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5099,7 +5039,6 @@
       <c r="G72" t="n">
         <v>0</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5110,7 +5049,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5156,7 +5095,6 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5167,7 +5105,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5213,7 +5151,6 @@
       <c r="G74" t="n">
         <v>0</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5224,7 +5161,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5270,7 +5207,6 @@
       <c r="G75" t="n">
         <v>0</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5281,7 +5217,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5327,7 +5263,6 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5338,7 +5273,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5384,7 +5319,6 @@
       <c r="G77" t="n">
         <v>0</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5395,7 +5329,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5441,7 +5375,6 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5452,7 +5385,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5498,7 +5431,6 @@
       <c r="G79" t="n">
         <v>119.74</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5509,7 +5441,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5555,7 +5487,6 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5566,7 +5497,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5612,7 +5543,6 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5623,7 +5553,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5669,7 +5599,6 @@
       <c r="G82" t="n">
         <v>0</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5680,7 +5609,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5726,7 +5655,6 @@
       <c r="G83" t="n">
         <v>0</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5737,7 +5665,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5783,7 +5711,6 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5794,7 +5721,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5840,7 +5767,6 @@
       <c r="G85" t="n">
         <v>0</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5851,7 +5777,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5897,7 +5823,6 @@
       <c r="G86" t="n">
         <v>0</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5908,7 +5833,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5954,7 +5879,6 @@
       <c r="G87" t="n">
         <v>0</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5965,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6011,7 +5935,6 @@
       <c r="G88" t="n">
         <v>0</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6022,7 +5945,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6068,7 +5991,6 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6079,7 +6001,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6125,7 +6047,6 @@
       <c r="G90" t="n">
         <v>92.76000000000001</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6136,7 +6057,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6182,7 +6103,6 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6193,7 +6113,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6239,7 +6159,6 @@
       <c r="G92" t="n">
         <v>0</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6250,7 +6169,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6296,7 +6215,6 @@
       <c r="G93" t="n">
         <v>0</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6307,7 +6225,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6353,7 +6271,6 @@
       <c r="G94" t="n">
         <v>0</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6364,7 +6281,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6410,7 +6327,6 @@
       <c r="G95" t="n">
         <v>0</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6421,7 +6337,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6467,7 +6383,6 @@
       <c r="G96" t="n">
         <v>0</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6478,7 +6393,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6524,7 +6439,6 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6535,7 +6449,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6581,7 +6495,6 @@
       <c r="G98" t="n">
         <v>0</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6592,7 +6505,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6638,7 +6551,6 @@
       <c r="G99" t="n">
         <v>0</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6649,7 +6561,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6695,7 +6607,6 @@
       <c r="G100" t="n">
         <v>0</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6706,7 +6617,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6752,7 +6663,6 @@
       <c r="G101" t="n">
         <v>0</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6763,7 +6673,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6809,7 +6719,6 @@
       <c r="G102" t="n">
         <v>0</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6820,7 +6729,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6866,7 +6775,6 @@
       <c r="G103" t="n">
         <v>0</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6877,7 +6785,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6923,7 +6831,6 @@
       <c r="G104" t="n">
         <v>0</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6934,7 +6841,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6980,7 +6887,6 @@
       <c r="G105" t="n">
         <v>0</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6991,7 +6897,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7037,7 +6943,6 @@
       <c r="G106" t="n">
         <v>0</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7048,7 +6953,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7094,7 +6999,6 @@
       <c r="G107" t="n">
         <v>0</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7105,7 +7009,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7151,7 +7055,6 @@
       <c r="G108" t="n">
         <v>0</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7162,7 +7065,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7208,7 +7111,6 @@
       <c r="G109" t="n">
         <v>0</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7219,7 +7121,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7265,7 +7167,6 @@
       <c r="G110" t="n">
         <v>0</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7276,7 +7177,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7322,7 +7223,6 @@
       <c r="G111" t="n">
         <v>0</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7333,7 +7233,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7379,7 +7279,6 @@
       <c r="G112" t="n">
         <v>7.28</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7390,7 +7289,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7436,7 +7335,6 @@
       <c r="G113" t="n">
         <v>8.17</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7447,7 +7345,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7493,7 +7391,6 @@
       <c r="G114" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7504,7 +7401,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7550,7 +7447,6 @@
       <c r="G115" t="n">
         <v>7.28</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7561,7 +7457,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7607,7 +7503,6 @@
       <c r="G116" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7618,7 +7513,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7664,7 +7559,6 @@
       <c r="G117" t="n">
         <v>9.06</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7675,7 +7569,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7721,7 +7615,6 @@
       <c r="G118" t="n">
         <v>7.28</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7732,7 +7625,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7778,7 +7671,6 @@
       <c r="G119" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7789,7 +7681,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7835,7 +7727,6 @@
       <c r="G120" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7846,7 +7737,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7892,7 +7783,6 @@
       <c r="G121" t="n">
         <v>9.06</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7903,7 +7793,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7949,7 +7839,6 @@
       <c r="G122" t="n">
         <v>7.28</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7960,7 +7849,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8006,7 +7895,6 @@
       <c r="G123" t="n">
         <v>8.17</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8017,7 +7905,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8063,7 +7951,6 @@
       <c r="G124" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8074,7 +7961,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8120,7 +8007,6 @@
       <c r="G125" t="n">
         <v>9.06</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8131,7 +8017,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8177,7 +8063,6 @@
       <c r="G126" t="n">
         <v>7.28</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8188,7 +8073,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8234,7 +8119,6 @@
       <c r="G127" t="n">
         <v>8.17</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8245,7 +8129,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8291,7 +8175,6 @@
       <c r="G128" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8302,7 +8185,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8348,7 +8231,6 @@
       <c r="G129" t="n">
         <v>9.06</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8359,7 +8241,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8405,7 +8287,6 @@
       <c r="G130" t="n">
         <v>7.28</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8416,7 +8297,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8462,7 +8343,6 @@
       <c r="G131" t="n">
         <v>8.17</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8473,7 +8353,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8519,7 +8399,6 @@
       <c r="G132" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8530,7 +8409,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8576,7 +8455,6 @@
       <c r="G133" t="n">
         <v>8.17</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8587,7 +8465,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8633,7 +8511,6 @@
       <c r="G134" t="n">
         <v>9.06</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8644,7 +8521,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8690,7 +8567,6 @@
       <c r="G135" t="n">
         <v>8.17</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8701,7 +8577,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8747,7 +8623,6 @@
       <c r="G136" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8758,7 +8633,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8804,7 +8679,6 @@
       <c r="G137" t="n">
         <v>9.06</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8815,7 +8689,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8861,7 +8735,6 @@
       <c r="G138" t="n">
         <v>8.17</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8872,7 +8745,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8918,7 +8791,6 @@
       <c r="G139" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8929,7 +8801,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8975,7 +8847,6 @@
       <c r="G140" t="n">
         <v>7.28</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8986,7 +8857,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9032,7 +8903,6 @@
       <c r="G141" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9043,7 +8913,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9089,7 +8959,6 @@
       <c r="G142" t="n">
         <v>7.28</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9100,7 +8969,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9146,7 +9015,6 @@
       <c r="G143" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9157,7 +9025,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9203,7 +9071,6 @@
       <c r="G144" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9214,7 +9081,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9260,7 +9127,6 @@
       <c r="G145" t="n">
         <v>0</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9271,7 +9137,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9317,7 +9183,6 @@
       <c r="G146" t="n">
         <v>0</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9328,7 +9193,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9374,7 +9239,6 @@
       <c r="G147" t="n">
         <v>0</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9385,7 +9249,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9431,7 +9295,6 @@
       <c r="G148" t="n">
         <v>9.06</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9442,7 +9305,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9488,7 +9351,6 @@
       <c r="G149" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9499,7 +9361,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9545,7 +9407,6 @@
       <c r="G150" t="n">
         <v>7.28</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9556,7 +9417,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9602,7 +9463,6 @@
       <c r="G151" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9613,7 +9473,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9659,7 +9519,6 @@
       <c r="G152" t="n">
         <v>9.06</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9670,7 +9529,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9716,7 +9575,6 @@
       <c r="G153" t="n">
         <v>7.28</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9727,7 +9585,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9773,7 +9631,6 @@
       <c r="G154" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9784,7 +9641,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9830,7 +9687,6 @@
       <c r="G155" t="n">
         <v>0</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9841,7 +9697,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9887,7 +9743,6 @@
       <c r="G156" t="n">
         <v>9.06</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9898,7 +9753,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9944,7 +9799,6 @@
       <c r="G157" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9955,7 +9809,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10001,7 +9855,6 @@
       <c r="G158" t="n">
         <v>7.28</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10012,7 +9865,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10058,7 +9911,6 @@
       <c r="G159" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10069,7 +9921,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10115,7 +9967,6 @@
       <c r="G160" t="n">
         <v>9.06</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10126,7 +9977,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10172,7 +10023,6 @@
       <c r="G161" t="n">
         <v>7.28</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10183,7 +10033,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10229,7 +10079,6 @@
       <c r="G162" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10240,7 +10089,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10286,7 +10135,6 @@
       <c r="G163" t="n">
         <v>0</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10297,7 +10145,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10343,7 +10191,6 @@
       <c r="G164" t="n">
         <v>0</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10354,7 +10201,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10400,7 +10247,6 @@
       <c r="G165" t="n">
         <v>0</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10411,7 +10257,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10457,7 +10303,6 @@
       <c r="G166" t="n">
         <v>0</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10468,7 +10313,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10514,7 +10359,6 @@
       <c r="G167" t="n">
         <v>0</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10525,7 +10369,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10571,7 +10415,6 @@
       <c r="G168" t="n">
         <v>0</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10582,7 +10425,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10628,7 +10471,6 @@
       <c r="G169" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10639,7 +10481,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10685,7 +10527,6 @@
       <c r="G170" t="n">
         <v>7.28</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10696,7 +10537,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10742,7 +10583,6 @@
       <c r="G171" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10753,7 +10593,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10799,7 +10639,6 @@
       <c r="G172" t="n">
         <v>9.06</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10810,7 +10649,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10856,7 +10695,6 @@
       <c r="G173" t="n">
         <v>7.28</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10867,7 +10705,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10913,7 +10751,6 @@
       <c r="G174" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10924,7 +10761,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10970,7 +10807,6 @@
       <c r="G175" t="n">
         <v>0</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10981,7 +10817,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11027,7 +10863,6 @@
       <c r="G176" t="n">
         <v>0</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11038,7 +10873,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11084,7 +10919,6 @@
       <c r="G177" t="n">
         <v>9.06</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11095,7 +10929,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11141,7 +10975,6 @@
       <c r="G178" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11152,7 +10985,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11198,7 +11031,6 @@
       <c r="G179" t="n">
         <v>7.28</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11209,7 +11041,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11255,7 +11087,6 @@
       <c r="G180" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11266,7 +11097,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11312,7 +11143,6 @@
       <c r="G181" t="n">
         <v>9.06</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11323,7 +11153,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11369,7 +11199,6 @@
       <c r="G182" t="n">
         <v>7.28</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11380,7 +11209,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11426,7 +11255,6 @@
       <c r="G183" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11437,7 +11265,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11483,7 +11311,6 @@
       <c r="G184" t="n">
         <v>0</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11494,7 +11321,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11540,7 +11367,6 @@
       <c r="G185" t="n">
         <v>9.06</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11551,7 +11377,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11597,7 +11423,6 @@
       <c r="G186" t="n">
         <v>7.28</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11608,7 +11433,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11654,7 +11479,6 @@
       <c r="G187" t="n">
         <v>8.17</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11665,7 +11489,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11711,7 +11535,6 @@
       <c r="G188" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11722,7 +11545,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11768,7 +11591,6 @@
       <c r="G189" t="n">
         <v>0</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11779,7 +11601,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11825,7 +11647,6 @@
       <c r="G190" t="n">
         <v>8.17</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11836,7 +11657,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11882,7 +11703,6 @@
       <c r="G191" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11893,7 +11713,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11939,7 +11759,6 @@
       <c r="G192" t="n">
         <v>9.06</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11950,7 +11769,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11996,7 +11815,6 @@
       <c r="G193" t="n">
         <v>7.28</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12007,7 +11825,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12053,7 +11871,6 @@
       <c r="G194" t="n">
         <v>8.17</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12064,7 +11881,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12110,7 +11927,6 @@
       <c r="G195" t="n">
         <v>9.06</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12121,7 +11937,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12167,7 +11983,6 @@
       <c r="G196" t="n">
         <v>7.28</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12178,7 +11993,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12224,7 +12039,6 @@
       <c r="G197" t="n">
         <v>8.17</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12235,7 +12049,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12281,7 +12095,6 @@
       <c r="G198" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12292,7 +12105,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12338,7 +12151,6 @@
       <c r="G199" t="n">
         <v>0</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12349,7 +12161,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12395,7 +12207,6 @@
       <c r="G200" t="n">
         <v>0</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12406,7 +12217,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12452,7 +12263,6 @@
       <c r="G201" t="n">
         <v>0</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12463,7 +12273,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -12509,7 +12319,6 @@
       <c r="G202" t="n">
         <v>9.06</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12520,7 +12329,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -12566,7 +12375,6 @@
       <c r="G203" t="n">
         <v>7.28</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12577,7 +12385,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -12623,7 +12431,6 @@
       <c r="G204" t="n">
         <v>8.17</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12634,7 +12441,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -12680,7 +12487,6 @@
       <c r="G205" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12691,7 +12497,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -12737,7 +12543,6 @@
       <c r="G206" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12748,7 +12553,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12794,7 +12599,6 @@
       <c r="G207" t="n">
         <v>16.33</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12805,7 +12609,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -12851,7 +12655,6 @@
       <c r="G208" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12862,7 +12665,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -12908,7 +12711,6 @@
       <c r="G209" t="n">
         <v>8.17</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12919,7 +12721,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -12965,7 +12767,6 @@
       <c r="G210" t="n">
         <v>7.28</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12976,7 +12777,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13022,7 +12823,6 @@
       <c r="G211" t="n">
         <v>8.17</v>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13033,7 +12833,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13079,7 +12879,6 @@
       <c r="G212" t="n">
         <v>7.28</v>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13090,7 +12889,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13136,7 +12935,6 @@
       <c r="G213" t="n">
         <v>7.28</v>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13147,7 +12945,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13193,7 +12991,6 @@
       <c r="G214" t="n">
         <v>8.17</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13204,7 +13001,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13250,7 +13047,6 @@
       <c r="G215" t="n">
         <v>9.06</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13261,7 +13057,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13307,7 +13103,6 @@
       <c r="G216" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13318,7 +13113,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -13364,7 +13159,6 @@
       <c r="G217" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13375,7 +13169,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -13421,7 +13215,6 @@
       <c r="G218" t="n">
         <v>9.06</v>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13432,7 +13225,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -13478,7 +13271,6 @@
       <c r="G219" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13489,7 +13281,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -13535,7 +13327,6 @@
       <c r="G220" t="n">
         <v>8.17</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13546,7 +13337,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -13592,7 +13383,6 @@
       <c r="G221" t="n">
         <v>8.17</v>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13603,7 +13393,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -13649,7 +13439,6 @@
       <c r="G222" t="n">
         <v>0</v>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13660,7 +13449,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -13706,7 +13495,6 @@
       <c r="G223" t="n">
         <v>0</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13717,7 +13505,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">

--- a/data/availability/projects/mountain-view/mountain-view-crystal.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-crystal.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Beach cabana</t>
+          <t>Beach Cabana</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>One Storey</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>One Storey</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Beach cabana</t>
+          <t>Beach Cabana</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>One Storey</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>One Storey</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
